--- a/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R64ce5da12df544ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R862dbb6fbd354a91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R7a34afdd1f604b7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Reac581d16e7f4328"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R7a34afdd1f604b7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Reac581d16e7f4328"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Ra82cd4ab8aa04489"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rc1469bcdb0f84e05"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Ra82cd4ab8aa04489"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rc1469bcdb0f84e05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rdf165483164946b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rf194a29c832d40ef"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rdf165483164946b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rf194a29c832d40ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rf59fb83a7e244d1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Ra4fd04a151eb4159"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rf59fb83a7e244d1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Ra4fd04a151eb4159"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R990f49e343ed4248"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R8afac7e40a244cf1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R990f49e343ed4248"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R8afac7e40a244cf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R28bdd37e9fd940c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rf87f2affd9834a59"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R28bdd37e9fd940c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rf87f2affd9834a59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R42fadda5da9b48dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Raa780f57df934f38"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R42fadda5da9b48dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Raa780f57df934f38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R0a52deceb9d54fa5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R6ac263ab389844a3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R0a52deceb9d54fa5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R6ac263ab389844a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Ra5813c7e7825495f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R0dbafe3a152a4b74"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Ra5813c7e7825495f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R0dbafe3a152a4b74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R758d73fcb0414a8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R4760f2767aca4353"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R758d73fcb0414a8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R4760f2767aca4353"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rd4fedda39d134438"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rc3b707409b8e450f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rd4fedda39d134438"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rc3b707409b8e450f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rad1b1cd4bc624c03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R839674354e6f4748"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rad1b1cd4bc624c03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R839674354e6f4748"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R5fe0c0a62c30430a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R163c9778e56944a1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R5fe0c0a62c30430a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R163c9778e56944a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R98050d9e26b74063"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rb49ffce09b1a4131"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R98050d9e26b74063"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rb49ffce09b1a4131"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R2ce9646a0baf4748"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R2a55ef90f2af4d5b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R2ce9646a0baf4748"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R2a55ef90f2af4d5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R8201c2e8711f446f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R3c4b8e69351542c8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R8201c2e8711f446f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R3c4b8e69351542c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rc048ca9e12c24422"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R66af01184d624cfd"/>
   </x:sheets>
 </x:workbook>
 </file>
